--- a/Zinc/5. Statistical data analysis/Identifying stream typology plots/Relative_freq_percentages_by_cluster.xlsx
+++ b/Zinc/5. Statistical data analysis/Identifying stream typology plots/Relative_freq_percentages_by_cluster.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -71,19 +71,13 @@
     <t xml:space="preserve">Perennial</t>
   </si>
   <si>
-    <t xml:space="preserve">Relative_elevation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1-10.5 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;2.1 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;10.5 m</t>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tributaries</t>
   </si>
 </sst>
 </file>
@@ -933,10 +927,10 @@
         <v>21</v>
       </c>
       <c r="D31" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
-        <v>33.0275229357798</v>
+        <v>91.743119266055</v>
       </c>
     </row>
     <row r="32">
@@ -944,16 +938,16 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="E32" t="n">
-        <v>25.6880733944954</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -961,16 +955,16 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D33" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="E33" t="n">
-        <v>33.0275229357798</v>
+        <v>73.4848484848485</v>
       </c>
     </row>
     <row r="34">
@@ -978,16 +972,16 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
         <v>21</v>
       </c>
       <c r="D34" t="n">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="E34" t="n">
-        <v>69.8412698412698</v>
+        <v>26.5151515151515</v>
       </c>
     </row>
     <row r="35">
@@ -995,135 +989,16 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>23.015873015873</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" t="n">
-        <v>9</v>
-      </c>
-      <c r="E36" t="n">
-        <v>7.14285714285714</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B37" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" t="n">
-        <v>97</v>
-      </c>
-      <c r="E37" t="n">
-        <v>73.4848484848485</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" t="n">
-        <v>25</v>
-      </c>
-      <c r="E38" t="n">
-        <v>18.9393939393939</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7</v>
-      </c>
-      <c r="E39" t="n">
-        <v>5.3030303030303</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2.27272727272727</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5.26315789473684</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" t="s">
-        <v>23</v>
-      </c>
-      <c r="D42" t="n">
-        <v>18</v>
-      </c>
-      <c r="E42" t="n">
-        <v>94.7368421052632</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/5. Statistical data analysis/Identifying stream typology plots/Relative_freq_percentages_by_cluster.xlsx
+++ b/Zinc/5. Statistical data analysis/Identifying stream typology plots/Relative_freq_percentages_by_cluster.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -51,15 +51,6 @@
   </si>
   <si>
     <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flow_state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flowing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">Regime</t>
@@ -434,10 +425,10 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>19.2660550458716</v>
+        <v>13.265306122449</v>
       </c>
     </row>
     <row r="3">
@@ -451,10 +442,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" t="n">
-        <v>52.2935779816514</v>
+        <v>56.1224489795918</v>
       </c>
     </row>
     <row r="4">
@@ -468,10 +459,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
-        <v>28.4403669724771</v>
+        <v>30.6122448979592</v>
       </c>
     </row>
     <row r="5">
@@ -488,7 +479,7 @@
         <v>68</v>
       </c>
       <c r="E5" t="n">
-        <v>53.968253968254</v>
+        <v>58.1196581196581</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +496,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6984126984127</v>
+        <v>13.6752136752137</v>
       </c>
     </row>
     <row r="7">
@@ -519,10 +510,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>33.3333333333333</v>
+        <v>28.2051282051282</v>
       </c>
     </row>
     <row r="8">
@@ -536,10 +527,10 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>31.0606060606061</v>
+        <v>29.9212598425197</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +547,7 @@
         <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>24.2424242424242</v>
+        <v>25.1968503937008</v>
       </c>
     </row>
     <row r="10">
@@ -570,10 +561,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" t="n">
-        <v>44.6969696969697</v>
+        <v>44.8818897637795</v>
       </c>
     </row>
     <row r="11">
@@ -584,13 +575,13 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>5.26315789473684</v>
+        <v>35.7142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -601,30 +592,30 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>26.3157894736842</v>
+        <v>64.2857142857143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>68.4210526315789</v>
+        <v>29.5918367346939</v>
       </c>
     </row>
     <row r="14">
@@ -635,13 +626,13 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="E14" t="n">
-        <v>89.9082568807339</v>
+        <v>70.4081632653061</v>
       </c>
     </row>
     <row r="15">
@@ -649,16 +640,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>10.0917431192661</v>
+        <v>4.27350427350427</v>
       </c>
     </row>
     <row r="16">
@@ -669,13 +660,13 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E16" t="n">
-        <v>92.0634920634921</v>
+        <v>95.7264957264957</v>
       </c>
     </row>
     <row r="17">
@@ -683,16 +674,16 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="E17" t="n">
-        <v>7.93650793650794</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -700,16 +691,16 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>127</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>96.2121212121212</v>
+        <v>92.8571428571429</v>
       </c>
     </row>
     <row r="19">
@@ -717,50 +708,50 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>3.78787878787879</v>
+        <v>7.14285714285714</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>78.9473684210526</v>
+        <v>9.18367346938776</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="E21" t="n">
-        <v>21.0526315789474</v>
+        <v>90.8163265306122</v>
       </c>
     </row>
     <row r="22">
@@ -768,16 +759,16 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="E22" t="n">
-        <v>35.7798165137615</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -785,16 +776,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E23" t="n">
-        <v>64.2201834862385</v>
+        <v>76.3779527559055</v>
       </c>
     </row>
     <row r="24">
@@ -802,16 +793,16 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E24" t="n">
-        <v>11.9047619047619</v>
+        <v>23.6220472440945</v>
       </c>
     </row>
     <row r="25">
@@ -819,185 +810,15 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="n">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>88.0952380952381</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.78787878787879</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" t="n">
-        <v>127</v>
-      </c>
-      <c r="E27" t="n">
-        <v>96.2121212121212</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="n">
-        <v>18</v>
-      </c>
-      <c r="E28" t="n">
-        <v>94.7368421052632</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5.26315789473684</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" t="n">
-        <v>9</v>
-      </c>
-      <c r="E30" t="n">
-        <v>8.25688073394496</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" t="n">
-        <v>100</v>
-      </c>
-      <c r="E31" t="n">
-        <v>91.743119266055</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" t="n">
-        <v>126</v>
-      </c>
-      <c r="E32" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" t="n">
-        <v>97</v>
-      </c>
-      <c r="E33" t="n">
-        <v>73.4848484848485</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" t="n">
-        <v>35</v>
-      </c>
-      <c r="E34" t="n">
-        <v>26.5151515151515</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" t="n">
-        <v>19</v>
-      </c>
-      <c r="E35" t="n">
         <v>100</v>
       </c>
     </row>
